--- a/output/pdf_financials_xlsx/GSRI.xlsx
+++ b/output/pdf_financials_xlsx/GSRI.xlsx
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.291289</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.940125</v>
       </c>
     </row>
     <row r="93">
@@ -3143,7 +3143,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSRI.xlsx
+++ b/output/pdf_financials_xlsx/GSRI.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002006</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000722</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-7.822634</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.493936</v>
+        <v>-4.495942</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.307459</v>
+        <v>-1.308181</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-7.822634</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.493936</v>
+        <v>-4.495942</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.307459</v>
+        <v>-1.308181</v>
       </c>
     </row>
     <row r="30">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSRI.xlsx
+++ b/output/pdf_financials_xlsx/GSRI.xlsx
@@ -2034,10 +2034,8 @@
       <c r="C99" s="3" t="n">
         <v>-4.493936</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-1.307459</v>
       </c>
     </row>
     <row r="100">
@@ -2052,10 +2050,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2065,15 +2061,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.050121</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010973</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.01863</v>
       </c>
     </row>
     <row r="102">
@@ -2088,10 +2082,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2106,10 +2098,8 @@
       <c r="C103" s="3" t="n">
         <v>0.67605</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0.146247</v>
       </c>
     </row>
     <row r="104">
@@ -2124,10 +2114,8 @@
       <c r="C104" s="3" t="n">
         <v>0.232273</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.327374</v>
       </c>
     </row>
     <row r="105">
@@ -2142,10 +2130,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2155,15 +2141,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.477519</v>
+        <v>-0.52764</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.908323</v>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.919296</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.492251</v>
       </c>
     </row>
     <row r="107">
@@ -2176,12 +2160,10 @@
         <v>2.640687</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.276171</v>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.552878</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.000536</v>
       </c>
     </row>
     <row r="108">
@@ -2196,10 +2178,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2214,10 +2194,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2232,10 +2210,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2250,10 +2226,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2268,10 +2242,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2286,10 +2258,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2304,10 +2274,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2322,10 +2290,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2340,10 +2306,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2358,10 +2322,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2376,10 +2338,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2396,10 +2356,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2414,10 +2372,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2432,10 +2388,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2450,10 +2404,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2468,10 +2420,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2486,10 +2436,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2504,10 +2452,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2522,10 +2468,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2562,10 +2506,8 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2582,10 +2524,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>0.78145</v>
       </c>
     </row>
     <row r="130">
@@ -2600,10 +2540,8 @@
       <c r="C130" s="3" t="n">
         <v>3.474363</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.175894</v>
       </c>
     </row>
     <row r="131">
@@ -2618,10 +2556,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2636,10 +2572,8 @@
       <c r="C132" s="3" t="n">
         <v>-3.298469</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>0.252971</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2588,8 @@
       <c r="C133" s="3" t="n">
         <v>0.175894</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.428865</v>
       </c>
     </row>
     <row r="134">
@@ -2672,10 +2604,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2690,10 +2620,8 @@
       <c r="C135" s="3" t="n">
         <v>-3.298469</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.528479</v>
       </c>
     </row>
   </sheetData>
@@ -2707,7 +2635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3357,7 +3285,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3365,16 +3293,16 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>-7.822634</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" s="5" t="n">
         <v>-4.493936</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="5" t="n">
+        <v>-1.307459</v>
       </c>
     </row>
     <row r="22">
@@ -3404,10 +3332,8 @@
       <c r="F22" s="5" t="n">
         <v>0.276171</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="5" t="n">
+        <v>0.000536</v>
       </c>
     </row>
     <row r="23">
@@ -3435,10 +3361,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="5" t="n">
+        <v>-0.004444</v>
       </c>
     </row>
     <row r="24">
@@ -3454,26 +3378,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>1.208769</v>
+          <t>Loss on settlement of liabilities</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G24" s="5" t="n">
+        <v>0.289333</v>
       </c>
     </row>
     <row r="25">
@@ -3484,25 +3404,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>-0.050121</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.010973</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.001304</v>
       </c>
     </row>
     <row r="26">
@@ -3518,24 +3440,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.426515</v>
+        <v>-0.050121</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.67605</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010973</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.01863</v>
       </c>
     </row>
     <row r="27">
@@ -3551,24 +3471,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-0.051004</v>
+        <v>-0.426515</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.232273</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.67605</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.146247</v>
       </c>
     </row>
     <row r="28">
@@ -3584,24 +3502,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-5.951747</v>
+        <v>-0.051004</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-3.298469</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.232273</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.327374</v>
       </c>
     </row>
     <row r="29">
@@ -3612,27 +3528,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Investing activity</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fish Creek Project option payments</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>-0.458769</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.951747</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-3.298469</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.528479</v>
       </c>
     </row>
     <row r="30">
@@ -3643,31 +3559,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing activity</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash used in investing activity</t>
+          <t>Proceeds from private placement</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>-0.458769</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="5" t="n">
+        <v>0.7414500000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3683,22 +3599,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of units</t>
+          <t>Proceeds from loan payable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" s="5" t="n">
-        <v>4.6</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="5" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="32">
@@ -3714,26 +3630,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.427718</v>
+        <v>4.172282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G32" s="5" t="n">
+        <v>0.78145</v>
       </c>
     </row>
     <row r="33">
@@ -3749,26 +3663,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
+          <t>Net change in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4.172282</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.238234</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-3.298469</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.252971</v>
       </c>
     </row>
     <row r="34">
@@ -3784,24 +3694,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Net change in cash and cash equivalents</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-2.238234</v>
+        <v>5.712597</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-3.298469</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.474363</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.175894</v>
       </c>
     </row>
     <row r="35">
@@ -3817,24 +3725,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Cash and cash equivalents, end of year</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>5.712597</v>
+        <v>3.474363</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3.474363</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.175894</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.428865</v>
       </c>
     </row>
     <row r="36">
@@ -3845,24 +3751,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
+          <t>Cash interest paid</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>3.474363</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.175894</v>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3883,12 +3793,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash interest paid</t>
+          <t>Cash income tax paid</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
+          <t>IncomeTaxPaidSupplementalData</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3920,14 +3830,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash income tax paid</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Fair value of shares issued for debt settlement</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -3938,10 +3844,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G38" s="5" t="n">
+        <v>0.5373329999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3952,27 +3856,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Broker’s warrants issued in private placement</t>
+          <t>Balance, July 31, 2023 6,602,846 19,500,324 4,078,046</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>0.206031</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>5.751771</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-17.826599</v>
       </c>
     </row>
     <row r="40">
@@ -3988,15 +3890,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 43,028,720 15,534,073 2,779,080</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Share-based compensation - - 276,171</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>8.219865</v>
+        <v>0.276171</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-10.093288</v>
+        <v>0.276171</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4017,22 +3923,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Units issued for cash 23,000,000 4,600,000 -</t>
+          <t>Reclassification of expired warrants from reserve to deficit - - (2,062,928)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>4.6</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G41" s="5" t="n">
+        <v>2.062928</v>
       </c>
     </row>
     <row r="42">
@@ -4048,22 +3954,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Share issuance costs - (633,749) 206,031</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>-0.427718</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-4.493936</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-4.493936</v>
       </c>
     </row>
     <row r="43">
@@ -4079,26 +3987,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 1,182,258</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>1.182258</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, July 31, 2024 6,602,846 19,500,324 2,291,289</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1.534006</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-20.257607</v>
       </c>
     </row>
     <row r="44">
@@ -4114,7 +4016,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Reversal of vested shares - - (89,323)</t>
+          <t>Shares issued pursuant to private placement 4,943,000 741,450 -</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4124,7 +4026,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.089323</v>
+        <v>0.7414500000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4145,19 +4047,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>-7.822634</v>
+          <t>Shares issued pursuant to settlement of liabilities 1,653,333 537,333 -</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-7.822634</v>
+        <v>0.5373329999999999</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4178,15 +4078,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 66,028,720 19,500,324 4,078,046</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>5.751771</v>
+          <t>Share-based compensation - - 536</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-17.826599</v>
+        <v>0.000536</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4207,26 +4113,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 276,171</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0.276171</v>
+          <t>Reclassification of expired stock options from reserve to deficit - - (1,145,669)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="5" t="n">
+        <v>1.145669</v>
       </c>
     </row>
     <row r="48">
@@ -4242,7 +4144,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reclassification of expired warrants - - (2,062,928)</t>
+          <t>Reclassification of expired warrants from reserve to deficit - - (206,031)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4251,13 +4153,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>2.062928</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.206031</v>
       </c>
     </row>
     <row r="49">
@@ -4273,518 +4175,534 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 66,028,720 19,500,324 2,291,289</t>
+          <t>Balance, July 31, 2025 13,199,179 20,779,107 940,125</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>1.534006</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>-20.257607</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.505866</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-20.213366</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bank fees</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.005433</v>
+        <v>-7.822634</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.005598</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.003416</v>
+        <v>-4.493936</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.056</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>1.208769</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activity</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Director and management fees 11</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0.07978300000000001</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0525</v>
+          <t>Fish Creek Project option payments</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>-0.458769</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activity</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 7,11</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>3.389537</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.506742</v>
+          <t>Cash used in investing activity</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.458769</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of units</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.05914</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.032508</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.047675</v>
+        <v>4.6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.206587</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.116596</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.065929</v>
+        <v>-0.427718</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Broker’s warrants issued in private placement</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.101635</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.097999</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.059932</v>
+        <v>0.206031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Balance, July 31, 2022 43,028,720 15,534,073 2,779,080</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.384325</v>
+        <v>8.219865</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.06401800000000001</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.015072</v>
+        <v>-10.093288</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Professional fees 11</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.291032</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.271989</v>
+          <t>Units issued for cash 23,000,000 4,600,000 -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share-based compensation 10(f),11</t>
+          <t>Share issuance costs - (633,749) 206,031</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.276171</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.000536</v>
+      <c r="E59" s="5" t="n">
+        <v>-0.427718</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Share-based compensation - - 1,182,258</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6.52629</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>4.479242</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>1.079791</v>
+        <v>1.182258</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Change in fair value of securities held for trading 6</t>
+          <t>Reversal of vested shares - - (89,323)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.004444</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.089323</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Net loss and comprehensive loss for the year - - -</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-0.08007499999999999</v>
+        <v>-7.822634</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.0167</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.057803</v>
+        <v>-7.822634</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Interest expense 9</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.001304</v>
+          <t>Balance, July 31, 2023 66,028,720 19,500,324 4,078,046</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>5.751771</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-17.826599</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Reclassification of expired warrants - - (2,062,928)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.002006</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.000722</v>
+        <v>2.062928</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loss on settlement of liabilities 10(b)</t>
+          <t>Balance, July 31, 2024 66,028,720 19,500,324 2,291,289</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>-0.289333</v>
+      <c r="E65" s="5" t="n">
+        <v>1.534006</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-20.257607</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4795,27 +4713,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Bank fees</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-7.822634</v>
+        <v>0.005433</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-4.493936</v>
+        <v>0.005598</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-1.307459</v>
+        <v>0.003416</v>
       </c>
     </row>
     <row r="67">
@@ -4826,17 +4740,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 1(c))</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4845,10 +4759,10 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-6.800000000000001e-07</v>
+        <v>0.126</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-1.8e-07</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="68">
@@ -4859,25 +4773,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 1(c))</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Director and management fees 11</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>6.602846</v>
+        <v>0.07978300000000001</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>7.324059</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="69">
@@ -4893,24 +4811,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Consulting fees 9</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0.17845</v>
+          <t>Exploration and evaluation 7,11</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.389537</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.506742</v>
       </c>
     </row>
     <row r="70">
@@ -4926,7 +4840,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Director and management fees 9</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4935,15 +4849,13 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.088629</v>
+        <v>0.05914</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.07978300000000001</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032508</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.047675</v>
       </c>
     </row>
     <row r="71">
@@ -4959,20 +4871,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 7, 9</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
-        <v>4.03989</v>
+        <v>0.206587</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>3.389537</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.116596</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.065929</v>
       </c>
     </row>
     <row r="72">
@@ -4988,24 +4902,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.279943</v>
+        <v>0.101635</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.291032</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.097999</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.059932</v>
       </c>
     </row>
     <row r="73">
@@ -5021,20 +4933,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share-based compensation 9</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
-        <v>1.182258</v>
+        <v>0.384325</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.276171</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06401800000000001</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.015072</v>
       </c>
     </row>
     <row r="74">
@@ -5045,27 +4959,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 7</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>-1.208769</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 11</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.291032</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.271989</v>
       </c>
     </row>
     <row r="75">
@@ -5076,29 +4992,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>-1.6e-07</v>
+          <t>Share-based compensation 10(f),11</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.276171</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.000536</v>
       </c>
     </row>
     <row r="76">
@@ -5109,22 +5021,526 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>6.52629</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>4.479242</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>1.079791</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Change in fair value of securities held for trading 6</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.004444</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.08007499999999999</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.057803</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Interest expense 9</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-0.001304</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.002006</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.000722</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Loss on settlement of liabilities 10(b)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.289333</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-7.822634</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-4.493936</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-1.307459</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Basic and diluted (Note 1(c))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-6.800000000000001e-07</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-1.8e-07</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Basic and diluted (Note 1(c))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>6.602846</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>7.324059</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Consulting fees 9</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.17845</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Director and management fees 9</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.088629</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.07978300000000001</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures 7, 9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>4.03989</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>3.389537</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Professional fees 9</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.279943</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.291032</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Share-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>1.182258</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.276171</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets 7</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>-1.208769</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>Basic and diluted</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>-1.6e-07</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
         <v>49.645158</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F92" s="5" t="n">
         <v>66.02872000000001</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
